--- a/docs/hardware/VermogensLijst.xlsx
+++ b/docs/hardware/VermogensLijst.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Component</t>
   </si>
@@ -33,16 +33,13 @@
     <t xml:space="preserve">P_gemiddelde (W)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kosten (€)</t>
-  </si>
-  <si>
     <t>Opmerkingen</t>
   </si>
   <si>
-    <t xml:space="preserve">Raspberry Pi 4B (4 GB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbruik zonder extra USB-loads; piek ≈ 15 W</t>
+    <t xml:space="preserve">Raspberry Pi Zero 2W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbruik zonder loads; piek ≈ 2.5 W</t>
   </si>
   <si>
     <t xml:space="preserve">Somfy LT50 Rolmotor</t>
@@ -60,13 +57,7 @@
     <t xml:space="preserve">HP EliteDesk 800 G1 SFF</t>
   </si>
   <si>
-    <t xml:space="preserve">ong 10 % CPU-belasting; idle ≈ 20–30 W</t>
-  </si>
-  <si>
-    <t>Drukknop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stroom alleen tijdens indrukken (verwaarloosbaar)</t>
+    <t xml:space="preserve">ong 60 % CPU-belasting; idle ≈ 20–30 W</t>
   </si>
   <si>
     <t>TOTAAL</t>
@@ -75,14 +66,14 @@
     <t>–</t>
   </si>
   <si>
-    <t xml:space="preserve">Typisch totaal = 283.8 W (motor actief); gemiddeld ≈ 30 W</t>
+    <t xml:space="preserve">Typisch = motor actief; gemiddeld = idle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -90,20 +81,70 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Courier New"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor theme="8" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor theme="4" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -111,22 +152,66 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
+    <xf fontId="3" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
+    <xf fontId="3" fillId="5" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="1" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="2" builtinId="22"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent1" xfId="4" builtinId="29"/>
+    <cellStyle name="60% - Accent1" xfId="5" builtinId="32"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -142,16 +227,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table1" ref="$A$1:$G$7">
-  <autoFilter ref="$A$1:$G$7"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table1" ref="$A$1:$F$7">
+  <autoFilter ref="$A$1:$F$7"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="Component"/>
     <tableColumn id="2" name="Spanning (V)"/>
     <tableColumn id="3" name="Stroom (A)"/>
     <tableColumn id="4" name="P_typisch (W)"/>
     <tableColumn id="5" name="P_gemiddelde (W)"/>
-    <tableColumn id="6" name="Kosten (€)"/>
-    <tableColumn id="7" name="Opmerkingen"/>
+    <tableColumn id="6" name="Opmerkingen"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -656,8 +740,7 @@
     <col bestFit="1" customWidth="1" min="3" max="3" width="14.61328125"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="18.04296875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="21.47265625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14.61328125"/>
-    <col customWidth="1" min="7" max="7" width="66.7109375"/>
+    <col customWidth="1" min="6" max="7" width="66.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -679,36 +762,32 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2">
         <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>0.69999999999999996</v>
+        <f>D2/B2</f>
+        <v>0.23999999999999999</v>
       </c>
       <c r="D2" s="2">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="E2" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="F2" s="2">
-        <v>64.120000000000005</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
+        <f>D2</f>
+        <v>1.2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2">
         <v>230</v>
@@ -717,21 +796,19 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="2">
-        <v>253</v>
+        <f>B3*C3</f>
+        <v>253.00000000000003</v>
       </c>
       <c r="E3" s="2">
         <v>0.25</v>
       </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -740,21 +817,19 @@
         <v>0.25</v>
       </c>
       <c r="D4" s="2">
+        <f>B4*C4</f>
         <v>1.25</v>
       </c>
       <c r="E4" s="2">
         <v>1.25</v>
       </c>
-      <c r="F4" s="2">
-        <v>30</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
         <v>230</v>
@@ -763,66 +838,41 @@
         <v>0.11</v>
       </c>
       <c r="D5" s="2">
-        <v>25</v>
+        <f>B5*C5</f>
+        <v>25.300000000000001</v>
       </c>
       <c r="E5" s="2">
         <v>25</v>
       </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4">
+        <f>SUM(D2:D5)</f>
+        <v>280.75</v>
+      </c>
+      <c r="E6" s="4">
+        <f>SUM(E2:E5)</f>
+        <v>27.699999999999999</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2">
-        <v>283.80000000000001</v>
-      </c>
-      <c r="E7" s="2">
-        <v>30</v>
-      </c>
-      <c r="F7" s="2">
-        <v>94.120000000000005</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
+    <row r="7" ht="14.25"/>
     <row r="8" ht="14.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
